--- a/public/reports/HDFCLIFE_NS_Financial_Model.xlsx
+++ b/public/reports/HDFCLIFE_NS_Financial_Model.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="557">
   <si>
     <t>HDFC Life Insurance Company Limited (HDFCLIFE.NS)</t>
   </si>
@@ -57,7 +57,7 @@
     <t>WITHHELD</t>
   </si>
   <si>
-    <t>Upside / (downside)</t>
+    <t>Model valuation spread vs price (an unaudited model output, not a rating; not independently audited)</t>
   </si>
   <si>
     <t>n/a</t>
@@ -192,19 +192,19 @@
     <t>Snapshot ID</t>
   </si>
   <si>
-    <t>snap_HDFCLIFE_NS_3849e666294a</t>
+    <t>snap_HDFCLIFE_NS_0a557c5b14ac</t>
   </si>
   <si>
     <t>Snapshot SHA-256</t>
   </si>
   <si>
-    <t>3849e666294ad5e4d918dbe82e3b5226c287ec6d9c9f31583467fd47db56c6e6</t>
+    <t>0a557c5b14acab60ef4c4df5984a755f25eeebca7aa5eebe90f673e1ccdf3cad</t>
   </si>
   <si>
     <t>Built at</t>
   </si>
   <si>
-    <t>2026-11-01T14:58:28.841Z</t>
+    <t>2026-11-01T15:06:00.542Z</t>
   </si>
   <si>
     <t>Analysis status</t>
@@ -270,7 +270,7 @@
     <t>Fair value per share</t>
   </si>
   <si>
-    <t>Upside / (downside) %</t>
+    <t>Model valuation spread vs price (an unaudited model output, not a rating; not independently audited) %</t>
   </si>
   <si>
     <t>v1 formula-trace coverage % (a different measure from "figures that reconcile" in the run-status table)</t>
@@ -750,7 +750,7 @@
     <t>Withheld: Linked three-statement forecast -- The forecast for archetype INSURANCE is built by a sector model that does not expose operating-company drivers; no generic three-statement model is forced onto it.</t>
   </si>
   <si>
-    <t>Withheld: DCF cross-check -- Not eligible by methodology: valuation methodology routes this archetype (INSURANCE) to EMBEDDED_VALUE and prohibits the consolidated FCFF DCF . It is not forced to populate a sheet, and no DCF stance is published.</t>
+    <t>Withheld: DCF cross-check -- Not eligible by methodology: valuation methodology routes this archetype (INSURANCE) to EMBEDDED_VALUE and prohibits the consolidated FCFF DCF . It is not forced to populate a sheet, and no DCF reading is published.</t>
   </si>
   <si>
     <t>Withheld: Reverse DCF -- a reverse DCF inverts a consolidated FCFF DCF, which this archetype's methodology prohibits</t>
@@ -936,7 +936,7 @@
     <t>ROE re-derived = margin x turnover x multiplier (live formula)</t>
   </si>
   <si>
-    <t>ACCOUNTING QUALITY (verdict UNAVAILABLE)</t>
+    <t>ACCOUNTING QUALITY (assessment UNAVAILABLE)</t>
   </si>
   <si>
     <t>Check</t>
@@ -1497,40 +1497,16 @@
     <t>Assumptions hash (12)</t>
   </si>
   <si>
-    <t>snap_HDFCLIFE_NS_3849e666294a  &lt;- THIS WORKBOOK</t>
+    <t>snap_HDFCLIFE_NS_0a557c5b14ac  &lt;- THIS WORKBOOK</t>
   </si>
   <si>
     <t>74234e98afe7</t>
   </si>
   <si>
-    <t>snap_HDFCLIFE_NS_e5fe7893b86e</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:58:28.802Z</t>
-  </si>
-  <si>
-    <t>snap_HDFCLIFE_NS_35f3ae9e6b2d</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:56:33.348Z</t>
-  </si>
-  <si>
-    <t>snap_HDFCLIFE_NS_55420367ed7c</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:56:33.309Z</t>
-  </si>
-  <si>
-    <t>snap_HDFCLIFE_NS_2450e95a7db1</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:54:08.073Z</t>
-  </si>
-  <si>
-    <t>snap_HDFCLIFE_NS_6165a7aa72e5</t>
-  </si>
-  <si>
-    <t>2026-11-01T14:54:08.021Z</t>
+    <t>snap_HDFCLIFE_NS_280285295d46</t>
+  </si>
+  <si>
+    <t>2026-11-01T15:06:00.491Z</t>
   </si>
   <si>
     <t>OVERRIDES APPLIED TO THIS WORKBOOK</t>
@@ -1608,7 +1584,7 @@
     <t>Difference</t>
   </si>
   <si>
-    <t>No DCF stance without a DCF</t>
+    <t>No DCF reading without a DCF</t>
   </si>
   <si>
     <t>VALUATION</t>
@@ -1617,7 +1593,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>no DCF ran and no stance is published</t>
+    <t>no DCF ran and no reading is published</t>
   </si>
   <si>
     <t>No bonus / split is classified as economic dilution</t>
@@ -1689,7 +1665,7 @@
     <t>DCF cross-check</t>
   </si>
   <si>
-    <t>Not eligible by methodology: valuation methodology routes this archetype (INSURANCE) to EMBEDDED_VALUE and prohibits the consolidated FCFF DCF . It is not forced to populate a sheet, and no DCF stance is published.</t>
+    <t>Not eligible by methodology: valuation methodology routes this archetype (INSURANCE) to EMBEDDED_VALUE and prohibits the consolidated FCFF DCF . It is not forced to populate a sheet, and no DCF reading is published.</t>
   </si>
   <si>
     <t>Reverse DCF</t>
@@ -1719,7 +1695,7 @@
     <t>SAVED RECORD AND VERIFIER RECEIPTS</t>
   </si>
   <si>
-    <t>This snapshot's saved record (provenance, publication states, discrepancies, peer selection, limits and every verifier receipt) is kept by FMB beside the exported files: GET /api/export/snapshot/snap_HDFCLIFE_NS_3849e666294a/record. Receipts are appended as verifiers run (workbook formula re-derivation, independent Monte Carlo), so they are read from the record, not stored in this file.</t>
+    <t>This snapshot's saved record (provenance, publication states, discrepancies, peer selection, limits and every verifier receipt) is kept by FMB beside the exported files: GET /api/export/snapshot/snap_HDFCLIFE_NS_0a557c5b14ac/record. Receipts are appended as verifiers run (workbook formula re-derivation, independent Monte Carlo), so they are read from the record, not stored in this file.</t>
   </si>
   <si>
     <t>Chart data (editable)</t>
@@ -8514,7 +8490,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
@@ -8633,178 +8609,62 @@
         <v>487</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>491</v>
       </c>
-      <c r="C8" s="14">
-        <v>524.9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>493</v>
       </c>
-      <c r="C9" s="14">
-        <v>524.9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B13" t="s">
         <v>494</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C13" t="s">
         <v>495</v>
       </c>
-      <c r="C10" s="14">
-        <v>524.9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>496</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B14" t="s">
         <v>497</v>
       </c>
-      <c r="C11" s="14">
-        <v>524.9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="C14" t="s">
         <v>498</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>501</v>
-      </c>
-      <c r="B17" t="s">
-        <v>502</v>
-      </c>
-      <c r="C17" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>504</v>
-      </c>
-      <c r="B18" t="s">
-        <v>505</v>
-      </c>
-      <c r="C18" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -8829,17 +8689,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -8851,7 +8711,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>382</v>
@@ -8860,35 +8720,35 @@
         <v>301</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>475</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -8903,19 +8763,19 @@
         <v>300</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>185</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>304</v>
@@ -8923,13 +8783,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="B10" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C10" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -8941,18 +8801,18 @@
         <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="B11" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="C11" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -8964,12 +8824,12 @@
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -8981,46 +8841,46 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="B16" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C16" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="D16" t="s">
         <v>191</v>
       </c>
       <c r="E16" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -9032,10 +8892,10 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="B19" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -9064,10 +8924,10 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="B23" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -9080,7 +8940,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="B25" t="s">
         <v>73</v>
@@ -9088,73 +8948,73 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B26" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="C26" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B27" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C27" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B28" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="C28" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B29" t="s">
+        <v>545</v>
+      </c>
+      <c r="C29" t="s">
         <v>546</v>
-      </c>
-      <c r="B29" t="s">
-        <v>553</v>
-      </c>
-      <c r="C29" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B30" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C30" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="B31" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C31" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -9166,7 +9026,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -9186,17 +9046,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -9206,7 +9066,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>
